--- a/Supply.xlsx
+++ b/Supply.xlsx
@@ -1,37 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26130"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ivlse-my.sharepoint.com/personal/erik_emilsson_ivl_se/Documents/Skrivbordet/temp_github/ELiMINATE_EU_MFA/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="16" documentId="11_F25DC773A252ABDACC1048DBE95E7B845BDE58EE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{531B5A83-6F58-4A78-A489-B867F6CCDB4E}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="11364" yWindow="8784" windowWidth="17916" windowHeight="14172" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -53,270 +31,278 @@
     <t>Longitude</t>
   </si>
   <si>
+    <t>Tonnes</t>
+  </si>
+  <si>
     <t>Vienna</t>
   </si>
   <si>
+    <t>Antwerp</t>
+  </si>
+  <si>
+    <t>Sofia</t>
+  </si>
+  <si>
+    <t>Zagreb</t>
+  </si>
+  <si>
+    <t>Prague</t>
+  </si>
+  <si>
+    <t>Copenhagen</t>
+  </si>
+  <si>
+    <t>Tallinn</t>
+  </si>
+  <si>
+    <t>Helsinki</t>
+  </si>
+  <si>
+    <t>Paris</t>
+  </si>
+  <si>
+    <t>Marseille</t>
+  </si>
+  <si>
+    <t>Berlin</t>
+  </si>
+  <si>
+    <t>Cologne</t>
+  </si>
+  <si>
+    <t>Düsseldorf</t>
+  </si>
+  <si>
+    <t>Munich</t>
+  </si>
+  <si>
+    <t>Frankfurt am Main</t>
+  </si>
+  <si>
+    <t>Stuttgart</t>
+  </si>
+  <si>
+    <t>Leipzig</t>
+  </si>
+  <si>
+    <t>Dortmund</t>
+  </si>
+  <si>
+    <t>Essen</t>
+  </si>
+  <si>
+    <t>Hanover</t>
+  </si>
+  <si>
+    <t>Nuremberg</t>
+  </si>
+  <si>
+    <t>Dresden</t>
+  </si>
+  <si>
+    <t>Hamburg</t>
+  </si>
+  <si>
+    <t>Bremen</t>
+  </si>
+  <si>
+    <t>Athens</t>
+  </si>
+  <si>
+    <t>Budapest</t>
+  </si>
+  <si>
+    <t>Rome</t>
+  </si>
+  <si>
+    <t>Milan</t>
+  </si>
+  <si>
+    <t>Naples</t>
+  </si>
+  <si>
+    <t>Turin</t>
+  </si>
+  <si>
+    <t>Palermo</t>
+  </si>
+  <si>
+    <t>Genoa</t>
+  </si>
+  <si>
+    <t>Riga</t>
+  </si>
+  <si>
+    <t>Vaduz</t>
+  </si>
+  <si>
+    <t>Vilnius</t>
+  </si>
+  <si>
+    <t>Luxembourg</t>
+  </si>
+  <si>
+    <t>Amsterdam</t>
+  </si>
+  <si>
+    <t>Rotterdam</t>
+  </si>
+  <si>
+    <t>The Hague</t>
+  </si>
+  <si>
+    <t>Oslo</t>
+  </si>
+  <si>
+    <t>Warsaw</t>
+  </si>
+  <si>
+    <t>Krakow</t>
+  </si>
+  <si>
+    <t>Łódź</t>
+  </si>
+  <si>
+    <t>Wrocław</t>
+  </si>
+  <si>
+    <t>Poznań</t>
+  </si>
+  <si>
+    <t>Lisbon</t>
+  </si>
+  <si>
+    <t>Bucharest</t>
+  </si>
+  <si>
+    <t>Belgrade</t>
+  </si>
+  <si>
+    <t>Bratislava</t>
+  </si>
+  <si>
+    <t>Ljublana</t>
+  </si>
+  <si>
+    <t>Madrid</t>
+  </si>
+  <si>
+    <t>Barcelona</t>
+  </si>
+  <si>
+    <t>Seville</t>
+  </si>
+  <si>
+    <t>Zaragoza</t>
+  </si>
+  <si>
+    <t>Málaga</t>
+  </si>
+  <si>
+    <t>Stockholm</t>
+  </si>
+  <si>
+    <t>Gothenburg</t>
+  </si>
+  <si>
+    <t>Zürich</t>
+  </si>
+  <si>
     <t>Austria</t>
   </si>
   <si>
-    <t>Antwerp</t>
-  </si>
-  <si>
     <t>Belgium</t>
   </si>
   <si>
-    <t>Sofia</t>
-  </si>
-  <si>
     <t>Bulgaria</t>
   </si>
   <si>
-    <t>Zagreb</t>
-  </si>
-  <si>
     <t>Croatia</t>
   </si>
   <si>
-    <t>Prague</t>
-  </si>
-  <si>
     <t>Czech Republic</t>
   </si>
   <si>
-    <t>Copenhagen</t>
-  </si>
-  <si>
     <t>Denmark</t>
   </si>
   <si>
-    <t>Tallinn</t>
-  </si>
-  <si>
     <t>Estonia</t>
   </si>
   <si>
-    <t>Helsinki</t>
-  </si>
-  <si>
     <t>Finland</t>
   </si>
   <si>
-    <t>Paris</t>
-  </si>
-  <si>
     <t>France</t>
   </si>
   <si>
-    <t>Marseille</t>
-  </si>
-  <si>
-    <t>Berlin</t>
-  </si>
-  <si>
     <t>Germany</t>
   </si>
   <si>
-    <t>Cologne</t>
-  </si>
-  <si>
-    <t>Düsseldorf</t>
-  </si>
-  <si>
-    <t>Munich</t>
-  </si>
-  <si>
-    <t>Frankfurt am Main</t>
-  </si>
-  <si>
-    <t>Stuttgart</t>
-  </si>
-  <si>
-    <t>Leipzig</t>
-  </si>
-  <si>
-    <t>Dortmund</t>
-  </si>
-  <si>
-    <t>Essen</t>
-  </si>
-  <si>
-    <t>Hanover</t>
-  </si>
-  <si>
-    <t>Nuremberg</t>
-  </si>
-  <si>
-    <t>Dresden</t>
-  </si>
-  <si>
-    <t>Hamburg</t>
-  </si>
-  <si>
-    <t>Bremen</t>
-  </si>
-  <si>
-    <t>Athens</t>
-  </si>
-  <si>
     <t>Greece</t>
   </si>
   <si>
-    <t>Budapest</t>
-  </si>
-  <si>
     <t>Hungary</t>
   </si>
   <si>
-    <t>Rome</t>
-  </si>
-  <si>
     <t>Italy</t>
   </si>
   <si>
-    <t>Milan</t>
-  </si>
-  <si>
-    <t>Naples</t>
-  </si>
-  <si>
-    <t>Turin</t>
-  </si>
-  <si>
-    <t>Palermo</t>
-  </si>
-  <si>
-    <t>Genoa</t>
-  </si>
-  <si>
-    <t>Riga</t>
-  </si>
-  <si>
     <t>Latvia</t>
   </si>
   <si>
-    <t>Vaduz</t>
-  </si>
-  <si>
     <t>Liechtenstein</t>
   </si>
   <si>
-    <t>Vilnius</t>
-  </si>
-  <si>
     <t>Lithuania</t>
   </si>
   <si>
-    <t>Luxembourg</t>
-  </si>
-  <si>
-    <t>Amsterdam</t>
-  </si>
-  <si>
     <t>Netherlands</t>
   </si>
   <si>
-    <t>Rotterdam</t>
-  </si>
-  <si>
-    <t>The Hague</t>
-  </si>
-  <si>
-    <t>Oslo</t>
-  </si>
-  <si>
     <t>Norway</t>
   </si>
   <si>
-    <t>Warsaw</t>
-  </si>
-  <si>
     <t>Poland</t>
   </si>
   <si>
-    <t>Krakow</t>
-  </si>
-  <si>
-    <t>Łódź</t>
-  </si>
-  <si>
-    <t>Wrocław</t>
-  </si>
-  <si>
-    <t>Poznań</t>
-  </si>
-  <si>
-    <t>Lisbon</t>
-  </si>
-  <si>
     <t>Portugal</t>
   </si>
   <si>
-    <t>Bucharest</t>
-  </si>
-  <si>
     <t>Romania</t>
   </si>
   <si>
-    <t>Belgrade</t>
-  </si>
-  <si>
     <t>Serbia</t>
   </si>
   <si>
-    <t>Bratislava</t>
-  </si>
-  <si>
     <t>Slovakia</t>
   </si>
   <si>
-    <t>Ljublana</t>
-  </si>
-  <si>
     <t>Slovenia</t>
   </si>
   <si>
-    <t>Madrid</t>
-  </si>
-  <si>
     <t>Spain</t>
   </si>
   <si>
-    <t>Barcelona</t>
-  </si>
-  <si>
-    <t>Seville</t>
-  </si>
-  <si>
-    <t>Zaragoza</t>
-  </si>
-  <si>
-    <t>Málaga</t>
-  </si>
-  <si>
-    <t>Stockholm</t>
-  </si>
-  <si>
     <t>Sweden</t>
   </si>
   <si>
-    <t>Gothenburg</t>
-  </si>
-  <si>
-    <t>Zürich</t>
-  </si>
-  <si>
     <t>Switzerland</t>
-  </si>
-  <si>
-    <t>Tonnes</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -332,7 +318,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -340,26 +326,36 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
 </styleSheet>
 </file>
 
@@ -374,44 +370,44 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546A"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ED7D31"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="FFC000"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70AD47"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563C1"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954F72"/>
+        <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -438,15 +434,14 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -473,7 +468,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -485,242 +479,263 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="35000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="80000">
               <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="40000">
               <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F59"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
+    <row r="1" spans="1:6">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C2" t="s">
         <v>6</v>
       </c>
-      <c r="C2" t="s">
-        <v>5</v>
-      </c>
       <c r="D2">
-        <v>48.212195520000002</v>
+        <v>48.21219552</v>
       </c>
       <c r="E2">
-        <v>16.376599030000001</v>
+        <v>16.37659903</v>
       </c>
       <c r="F2">
-        <f ca="1">200*RAND()</f>
-        <v>44.964410105485882</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+        <v>4496.441010548589</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
       <c r="A3" t="s">
         <v>7</v>
       </c>
       <c r="B3" t="s">
-        <v>8</v>
+        <v>65</v>
       </c>
       <c r="C3" t="s">
         <v>7</v>
       </c>
       <c r="D3">
-        <v>51.212183119999999</v>
+        <v>51.21218312</v>
       </c>
       <c r="E3">
-        <v>4.4087702950000001</v>
+        <v>4.408770295</v>
       </c>
       <c r="F3">
-        <f t="shared" ref="F3:F59" ca="1" si="0">200*RAND()</f>
-        <v>27.134739717715917</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+        <v>2713.473971771592</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
       <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>66</v>
+      </c>
+      <c r="C4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4">
+        <v>42.6966725</v>
+      </c>
+      <c r="E4">
+        <v>23.33497505</v>
+      </c>
+      <c r="F4">
+        <v>10810.19093043366</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" t="s">
         <v>9</v>
       </c>
-      <c r="B4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" t="s">
+      <c r="B5" t="s">
+        <v>67</v>
+      </c>
+      <c r="C5" t="s">
         <v>9</v>
-      </c>
-      <c r="D4">
-        <v>42.696672499999998</v>
-      </c>
-      <c r="E4">
-        <v>23.334975050000001</v>
-      </c>
-      <c r="F4">
-        <f t="shared" ca="1" si="0"/>
-        <v>108.10190930433656</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5" t="s">
-        <v>11</v>
       </c>
       <c r="D5">
         <v>45.79497465</v>
@@ -729,19 +744,18 @@
         <v>15.97996172</v>
       </c>
       <c r="F5">
-        <f t="shared" ca="1" si="0"/>
-        <v>188.81972219565145</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+        <v>18881.97221956514</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
       <c r="A6" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B6" t="s">
-        <v>14</v>
+        <v>68</v>
       </c>
       <c r="C6" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D6">
         <v>50.0756649</v>
@@ -750,61 +764,58 @@
         <v>14.43016804</v>
       </c>
       <c r="F6">
-        <f t="shared" ca="1" si="0"/>
-        <v>154.96210037346586</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+        <v>15496.21003734659</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
       <c r="A7" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>16</v>
+        <v>69</v>
       </c>
       <c r="C7" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D7">
-        <v>55.671102759999997</v>
+        <v>55.67110276</v>
       </c>
       <c r="E7">
-        <v>12.577484999999999</v>
+        <v>12.577485</v>
       </c>
       <c r="F7">
-        <f t="shared" ca="1" si="0"/>
-        <v>44.500465640853463</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+        <v>4450.046564085346</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
       <c r="A8" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B8" t="s">
-        <v>18</v>
+        <v>70</v>
       </c>
       <c r="C8" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="D8">
-        <v>59.424197030000002</v>
+        <v>59.42419703</v>
       </c>
       <c r="E8">
-        <v>24.786154400000001</v>
+        <v>24.7861544</v>
       </c>
       <c r="F8">
-        <f t="shared" ca="1" si="0"/>
-        <v>102.6844727645458</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+        <v>10268.44727645458</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
       <c r="A9" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="B9" t="s">
-        <v>20</v>
+        <v>71</v>
       </c>
       <c r="C9" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="D9">
         <v>60.22303213</v>
@@ -813,838 +824,798 @@
         <v>24.9085641</v>
       </c>
       <c r="F9">
-        <f t="shared" ca="1" si="0"/>
-        <v>2.1361547616516319</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+        <v>213.6154761651632</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
       <c r="A10" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>22</v>
+        <v>72</v>
       </c>
       <c r="C10" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="D10">
         <v>48.79637185</v>
       </c>
       <c r="E10">
-        <v>2.3444475319999998</v>
+        <v>2.344447532</v>
       </c>
       <c r="F10">
-        <f t="shared" ca="1" si="0"/>
-        <v>196.25658748094094</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+        <v>19625.65874809409</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
       <c r="A11" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="B11" t="s">
-        <v>22</v>
+        <v>72</v>
       </c>
       <c r="C11" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="D11">
-        <v>43.340483470000002</v>
+        <v>43.34048347</v>
       </c>
       <c r="E11">
         <v>5.376756833</v>
       </c>
       <c r="F11">
-        <f t="shared" ca="1" si="0"/>
-        <v>144.24976039217813</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+        <v>14424.97603921781</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
       <c r="A12" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="B12" t="s">
-        <v>25</v>
+        <v>73</v>
       </c>
       <c r="C12" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="D12">
-        <v>52.469756369999999</v>
+        <v>52.46975637</v>
       </c>
       <c r="E12">
         <v>13.38552309</v>
       </c>
       <c r="F12">
-        <f t="shared" ca="1" si="0"/>
-        <v>179.26617987478218</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+        <v>17926.61798747822</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
       <c r="A13" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="B13" t="s">
-        <v>25</v>
+        <v>73</v>
       </c>
       <c r="C13" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="D13">
-        <v>50.940737069999997</v>
+        <v>50.94073707</v>
       </c>
       <c r="E13">
-        <v>6.9386991120000001</v>
+        <v>6.938699112</v>
       </c>
       <c r="F13">
-        <f t="shared" ca="1" si="0"/>
-        <v>111.99353056925322</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+        <v>11199.35305692532</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
       <c r="A14" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="B14" t="s">
-        <v>25</v>
+        <v>73</v>
       </c>
       <c r="C14" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="D14">
-        <v>51.215177850000003</v>
+        <v>51.21517785</v>
       </c>
       <c r="E14">
-        <v>6.8014629629999996</v>
+        <v>6.801462963</v>
       </c>
       <c r="F14">
-        <f t="shared" ca="1" si="0"/>
-        <v>17.582107074735042</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+        <v>1758.210707473504</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
       <c r="A15" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="B15" t="s">
-        <v>25</v>
+        <v>73</v>
       </c>
       <c r="C15" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="D15">
-        <v>48.140766890000002</v>
+        <v>48.14076689</v>
       </c>
       <c r="E15">
         <v>11.53464567</v>
       </c>
       <c r="F15">
-        <f t="shared" ca="1" si="0"/>
-        <v>19.601363943651773</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+        <v>1960.136394365177</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
       <c r="A16" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="B16" t="s">
-        <v>25</v>
+        <v>73</v>
       </c>
       <c r="C16" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="D16">
-        <v>50.114949950000003</v>
+        <v>50.11494995</v>
       </c>
       <c r="E16">
-        <v>8.6709011589999996</v>
+        <v>8.670901159</v>
       </c>
       <c r="F16">
-        <f t="shared" ca="1" si="0"/>
-        <v>192.96219726549049</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+        <v>19296.21972654905</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
       <c r="A17" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="B17" t="s">
-        <v>25</v>
+        <v>73</v>
       </c>
       <c r="C17" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="D17">
-        <v>48.809476660000001</v>
+        <v>48.80947666</v>
       </c>
       <c r="E17">
-        <v>9.1841374390000006</v>
+        <v>9.184137439000001</v>
       </c>
       <c r="F17">
-        <f t="shared" ca="1" si="0"/>
-        <v>165.11025233375412</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+        <v>16511.02523337541</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
       <c r="A18" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="B18" t="s">
-        <v>25</v>
+        <v>73</v>
       </c>
       <c r="C18" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="D18">
-        <v>51.344088229999997</v>
+        <v>51.34408823</v>
       </c>
       <c r="E18">
         <v>12.37026562</v>
       </c>
       <c r="F18">
-        <f t="shared" ca="1" si="0"/>
-        <v>91.252750358198995</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+        <v>9125.275035819899</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
       <c r="A19" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="B19" t="s">
+        <v>73</v>
+      </c>
+      <c r="C19" t="s">
+        <v>23</v>
+      </c>
+      <c r="D19">
+        <v>51.49898287</v>
+      </c>
+      <c r="E19">
+        <v>7.46906929</v>
+      </c>
+      <c r="F19">
+        <v>15454.22235816558</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="A20" t="s">
+        <v>24</v>
+      </c>
+      <c r="B20" t="s">
+        <v>73</v>
+      </c>
+      <c r="C20" t="s">
+        <v>24</v>
+      </c>
+      <c r="D20">
+        <v>51.45491743</v>
+      </c>
+      <c r="E20">
+        <v>7.043338947</v>
+      </c>
+      <c r="F20">
+        <v>3523.230835605451</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
+      <c r="A21" t="s">
         <v>25</v>
       </c>
-      <c r="C19" t="s">
-        <v>32</v>
-      </c>
-      <c r="D19">
-        <v>51.498982869999999</v>
-      </c>
-      <c r="E19">
-        <v>7.4690692900000002</v>
-      </c>
-      <c r="F19">
-        <f t="shared" ca="1" si="0"/>
-        <v>154.54222358165578</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A20" t="s">
-        <v>33</v>
-      </c>
-      <c r="B20" t="s">
+      <c r="B21" t="s">
+        <v>73</v>
+      </c>
+      <c r="C21" t="s">
         <v>25</v>
       </c>
-      <c r="C20" t="s">
-        <v>33</v>
-      </c>
-      <c r="D20">
-        <v>51.454917430000002</v>
-      </c>
-      <c r="E20">
-        <v>7.0433389469999996</v>
-      </c>
-      <c r="F20">
-        <f t="shared" ca="1" si="0"/>
-        <v>35.23230835605451</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A21" t="s">
-        <v>34</v>
-      </c>
-      <c r="B21" t="s">
-        <v>25</v>
-      </c>
-      <c r="C21" t="s">
-        <v>34</v>
-      </c>
       <c r="D21">
-        <v>52.345938539999999</v>
+        <v>52.34593854</v>
       </c>
       <c r="E21">
-        <v>9.7188024189999993</v>
+        <v>9.718802418999999</v>
       </c>
       <c r="F21">
-        <f t="shared" ca="1" si="0"/>
-        <v>26.026019190148418</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
+        <v>2602.601919014842</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6">
       <c r="A22" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="B22" t="s">
-        <v>25</v>
+        <v>73</v>
       </c>
       <c r="C22" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D22">
-        <v>49.428062140000002</v>
+        <v>49.42806214</v>
       </c>
       <c r="E22">
         <v>11.06311724</v>
       </c>
       <c r="F22">
-        <f t="shared" ca="1" si="0"/>
-        <v>48.277983898192204</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
+        <v>4827.798389819221</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6">
       <c r="A23" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="B23" t="s">
-        <v>25</v>
+        <v>73</v>
       </c>
       <c r="C23" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="D23">
-        <v>51.008003619999997</v>
+        <v>51.00800362</v>
       </c>
       <c r="E23">
         <v>13.72864468</v>
       </c>
       <c r="F23">
-        <f t="shared" ca="1" si="0"/>
-        <v>58.506432600217281</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
+        <v>5850.643260021728</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6">
       <c r="A24" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="B24" t="s">
-        <v>25</v>
+        <v>73</v>
       </c>
       <c r="C24" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="D24">
-        <v>53.549256059999998</v>
+        <v>53.54925606</v>
       </c>
       <c r="E24">
-        <v>9.9006175649999992</v>
+        <v>9.900617564999999</v>
       </c>
       <c r="F24">
-        <f t="shared" ca="1" si="0"/>
-        <v>173.41812168569641</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
+        <v>17341.81216856964</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6">
       <c r="A25" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="B25" t="s">
-        <v>25</v>
+        <v>73</v>
       </c>
       <c r="C25" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="D25">
         <v>53.11652119</v>
       </c>
       <c r="E25">
-        <v>8.8122783099999999</v>
+        <v>8.81227831</v>
       </c>
       <c r="F25">
-        <f t="shared" ca="1" si="0"/>
-        <v>198.26226136776762</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
+        <v>19826.22613677676</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6">
       <c r="A26" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="B26" t="s">
-        <v>40</v>
+        <v>74</v>
       </c>
       <c r="C26" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="D26">
-        <v>38.041161090000003</v>
+        <v>38.04116109</v>
       </c>
       <c r="E26">
-        <v>23.803824389999999</v>
+        <v>23.80382439</v>
       </c>
       <c r="F26">
-        <f t="shared" ca="1" si="0"/>
-        <v>177.94002826830712</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
+        <v>17794.00282683071</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6">
       <c r="A27" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="B27" t="s">
-        <v>42</v>
+        <v>75</v>
       </c>
       <c r="C27" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="D27">
-        <v>47.466226229999997</v>
+        <v>47.46622623</v>
       </c>
       <c r="E27">
-        <v>19.016133050000001</v>
+        <v>19.01613305</v>
       </c>
       <c r="F27">
-        <f t="shared" ca="1" si="0"/>
-        <v>182.27880211964774</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
+        <v>18227.88021196477</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6">
       <c r="A28" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="B28" t="s">
-        <v>44</v>
+        <v>76</v>
       </c>
       <c r="C28" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="D28">
-        <v>41.958031579999997</v>
+        <v>41.95803158</v>
       </c>
       <c r="E28">
         <v>12.57990682</v>
       </c>
       <c r="F28">
-        <f t="shared" ca="1" si="0"/>
-        <v>82.360008894181817</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
+        <v>8236.000889418181</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6">
       <c r="A29" t="s">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="B29" t="s">
-        <v>44</v>
+        <v>76</v>
       </c>
       <c r="C29" t="s">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="D29">
-        <v>45.516011059999997</v>
+        <v>45.51601106</v>
       </c>
       <c r="E29">
-        <v>9.1203607509999998</v>
+        <v>9.120360751</v>
       </c>
       <c r="F29">
-        <f t="shared" ca="1" si="0"/>
-        <v>79.328307937899353</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
+        <v>7932.830793789935</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6">
       <c r="A30" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="B30" t="s">
-        <v>44</v>
+        <v>76</v>
       </c>
       <c r="C30" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="D30">
         <v>40.84840002</v>
       </c>
       <c r="E30">
-        <v>14.313997949999999</v>
+        <v>14.31399795</v>
       </c>
       <c r="F30">
-        <f t="shared" ca="1" si="0"/>
-        <v>64.528099518435795</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
+        <v>6452.809951843579</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6">
       <c r="A31" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="B31" t="s">
-        <v>44</v>
+        <v>76</v>
       </c>
       <c r="C31" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="D31">
-        <v>44.970992320000001</v>
+        <v>44.97099232</v>
       </c>
       <c r="E31">
-        <v>7.7024445740000003</v>
+        <v>7.702444574</v>
       </c>
       <c r="F31">
-        <f t="shared" ca="1" si="0"/>
-        <v>4.2259570908388611</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
+        <v>422.5957090838861</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6">
       <c r="A32" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="B32" t="s">
-        <v>44</v>
+        <v>76</v>
       </c>
       <c r="C32" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="D32">
-        <v>38.093674470000003</v>
+        <v>38.09367447</v>
       </c>
       <c r="E32">
         <v>13.33917937</v>
       </c>
       <c r="F32">
-        <f t="shared" ca="1" si="0"/>
-        <v>112.7065577394368</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
+        <v>11270.65577394368</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6">
       <c r="A33" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="B33" t="s">
-        <v>44</v>
+        <v>76</v>
       </c>
       <c r="C33" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="D33">
-        <v>44.432752630000003</v>
+        <v>44.43275263</v>
       </c>
       <c r="E33">
-        <v>8.9606804899999997</v>
+        <v>8.96068049</v>
       </c>
       <c r="F33">
-        <f t="shared" ca="1" si="0"/>
-        <v>137.96335176798195</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
+        <v>13796.33517679819</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6">
       <c r="A34" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="B34" t="s">
-        <v>51</v>
+        <v>77</v>
       </c>
       <c r="C34" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="D34">
-        <v>56.846309210000001</v>
+        <v>56.84630921</v>
       </c>
       <c r="E34">
-        <v>24.396187090000002</v>
+        <v>24.39618709</v>
       </c>
       <c r="F34">
-        <f t="shared" ca="1" si="0"/>
-        <v>61.34387655528721</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
+        <v>6134.387655528721</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6">
       <c r="A35" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="B35" t="s">
-        <v>53</v>
+        <v>78</v>
       </c>
       <c r="C35" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="D35">
-        <v>47.155432210000001</v>
+        <v>47.15543221</v>
       </c>
       <c r="E35">
-        <v>9.5103569310000005</v>
+        <v>9.510356931</v>
       </c>
       <c r="F35">
-        <f t="shared" ca="1" si="0"/>
-        <v>148.3586919508613</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
+        <v>14835.86919508613</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6">
       <c r="A36" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="B36" t="s">
-        <v>55</v>
+        <v>79</v>
       </c>
       <c r="C36" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="D36">
-        <v>54.668795129999999</v>
+        <v>54.66879513</v>
       </c>
       <c r="E36">
-        <v>25.237573099999999</v>
+        <v>25.2375731</v>
       </c>
       <c r="F36">
-        <f t="shared" ca="1" si="0"/>
-        <v>29.438068979977693</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
+        <v>2943.806897997769</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6">
       <c r="A37" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="B37" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="C37" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="D37">
-        <v>49.819037639999998</v>
+        <v>49.81903764</v>
       </c>
       <c r="E37">
-        <v>6.0983639700000003</v>
+        <v>6.09836397</v>
       </c>
       <c r="F37">
-        <f t="shared" ca="1" si="0"/>
-        <v>168.35159797698429</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
+        <v>16835.15979769843</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6">
       <c r="A38" t="s">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="B38" t="s">
-        <v>58</v>
+        <v>80</v>
       </c>
       <c r="C38" t="s">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="D38">
-        <v>52.338693390000003</v>
+        <v>52.33869339</v>
       </c>
       <c r="E38">
-        <v>4.8421581610000004</v>
+        <v>4.842158161</v>
       </c>
       <c r="F38">
-        <f t="shared" ca="1" si="0"/>
-        <v>80.677946459670252</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
+        <v>8067.794645967026</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6">
       <c r="A39" t="s">
-        <v>59</v>
+        <v>43</v>
       </c>
       <c r="B39" t="s">
-        <v>58</v>
+        <v>80</v>
       </c>
       <c r="C39" t="s">
-        <v>59</v>
+        <v>43</v>
       </c>
       <c r="D39">
         <v>51.95075027</v>
       </c>
       <c r="E39">
-        <v>4.5294570099999998</v>
+        <v>4.52945701</v>
       </c>
       <c r="F39">
-        <f t="shared" ca="1" si="0"/>
-        <v>32.459897666361506</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
+        <v>3245.989766636151</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6">
       <c r="A40" t="s">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="B40" t="s">
-        <v>58</v>
+        <v>80</v>
       </c>
       <c r="C40" t="s">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="D40">
-        <v>52.062289929999999</v>
+        <v>52.06228993</v>
       </c>
       <c r="E40">
-        <v>4.3753405729999999</v>
+        <v>4.375340573</v>
       </c>
       <c r="F40">
-        <f t="shared" ca="1" si="0"/>
-        <v>66.045228504100834</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
+        <v>6604.522850410083</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6">
       <c r="A41" t="s">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="B41" t="s">
-        <v>62</v>
+        <v>81</v>
       </c>
       <c r="C41" t="s">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="D41">
-        <v>59.902028369999996</v>
+        <v>59.90202837</v>
       </c>
       <c r="E41">
-        <v>10.781292929999999</v>
+        <v>10.78129293</v>
       </c>
       <c r="F41">
-        <f t="shared" ca="1" si="0"/>
-        <v>199.29491084141856</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
+        <v>19929.49108414186</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6">
       <c r="A42" t="s">
-        <v>63</v>
+        <v>46</v>
       </c>
       <c r="B42" t="s">
-        <v>64</v>
+        <v>82</v>
       </c>
       <c r="C42" t="s">
-        <v>63</v>
+        <v>46</v>
       </c>
       <c r="D42">
-        <v>52.138805640000001</v>
+        <v>52.13880564</v>
       </c>
       <c r="E42">
         <v>20.9892915</v>
       </c>
       <c r="F42">
-        <f t="shared" ca="1" si="0"/>
-        <v>28.694432815235004</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
+        <v>2869.4432815235</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6">
       <c r="A43" t="s">
-        <v>65</v>
+        <v>47</v>
       </c>
       <c r="B43" t="s">
-        <v>64</v>
+        <v>82</v>
       </c>
       <c r="C43" t="s">
-        <v>65</v>
+        <v>47</v>
       </c>
       <c r="D43">
-        <v>50.086294520000003</v>
+        <v>50.08629452</v>
       </c>
       <c r="E43">
-        <v>19.954955909999999</v>
+        <v>19.95495591</v>
       </c>
       <c r="F43">
-        <f t="shared" ca="1" si="0"/>
-        <v>117.77728790291656</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
+        <v>11777.72879029166</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6">
       <c r="A44" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="B44" t="s">
-        <v>64</v>
+        <v>82</v>
       </c>
       <c r="C44" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="D44">
-        <v>51.726828009999998</v>
+        <v>51.72682801</v>
       </c>
       <c r="E44">
-        <v>19.447777370000001</v>
+        <v>19.44777737</v>
       </c>
       <c r="F44">
-        <f t="shared" ca="1" si="0"/>
-        <v>148.90217756652768</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
+        <v>14890.21775665277</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6">
       <c r="A45" t="s">
-        <v>67</v>
+        <v>49</v>
       </c>
       <c r="B45" t="s">
-        <v>64</v>
+        <v>82</v>
       </c>
       <c r="C45" t="s">
-        <v>67</v>
+        <v>49</v>
       </c>
       <c r="D45">
-        <v>51.165677090000003</v>
+        <v>51.16567709</v>
       </c>
       <c r="E45">
-        <v>17.028063929999998</v>
+        <v>17.02806393</v>
       </c>
       <c r="F45">
-        <f t="shared" ca="1" si="0"/>
-        <v>175.51950420432379</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
+        <v>17551.95042043238</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6">
       <c r="A46" t="s">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="B46" t="s">
-        <v>64</v>
+        <v>82</v>
       </c>
       <c r="C46" t="s">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="D46">
-        <v>52.350582170000003</v>
+        <v>52.35058217</v>
       </c>
       <c r="E46">
-        <v>16.760192180000001</v>
+        <v>16.76019218</v>
       </c>
       <c r="F46">
-        <f t="shared" ca="1" si="0"/>
-        <v>186.03214894662847</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
+        <v>18603.21489466285</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6">
       <c r="A47" t="s">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="B47" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="C47" t="s">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="D47">
         <v>38.72320526</v>
       </c>
       <c r="E47">
-        <v>-9.1755604430000002</v>
+        <v>-9.175560443</v>
       </c>
       <c r="F47">
-        <f t="shared" ca="1" si="0"/>
-        <v>37.082771507326065</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
+        <v>3708.277150732607</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6">
       <c r="A48" t="s">
-        <v>71</v>
+        <v>52</v>
       </c>
       <c r="B48" t="s">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="C48" t="s">
-        <v>71</v>
+        <v>52</v>
       </c>
       <c r="D48">
-        <v>44.428850939999997</v>
+        <v>44.42885094</v>
       </c>
       <c r="E48">
         <v>26.10398193</v>
       </c>
       <c r="F48">
-        <f t="shared" ca="1" si="0"/>
-        <v>99.973072017837893</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
+        <v>9997.307201783789</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6">
       <c r="A49" t="s">
-        <v>73</v>
+        <v>53</v>
       </c>
       <c r="B49" t="s">
-        <v>74</v>
+        <v>85</v>
       </c>
       <c r="C49" t="s">
-        <v>73</v>
+        <v>53</v>
       </c>
       <c r="D49">
         <v>44.79776245</v>
@@ -1653,218 +1624,207 @@
         <v>20.45058388</v>
       </c>
       <c r="F49">
-        <f t="shared" ca="1" si="0"/>
-        <v>57.362167181525251</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
+        <v>5736.216718152526</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6">
       <c r="A50" t="s">
-        <v>75</v>
+        <v>54</v>
       </c>
       <c r="B50" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="C50" t="s">
-        <v>75</v>
+        <v>54</v>
       </c>
       <c r="D50">
-        <v>48.130983030000003</v>
+        <v>48.13098303</v>
       </c>
       <c r="E50">
         <v>17.13001534</v>
       </c>
       <c r="F50">
-        <f t="shared" ca="1" si="0"/>
-        <v>131.99765471332424</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
+        <v>13199.76547133242</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6">
       <c r="A51" t="s">
-        <v>77</v>
+        <v>55</v>
       </c>
       <c r="B51" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="C51" t="s">
-        <v>77</v>
+        <v>55</v>
       </c>
       <c r="D51">
-        <v>46.013797859999997</v>
+        <v>46.01379786</v>
       </c>
       <c r="E51">
         <v>14.55725331</v>
       </c>
       <c r="F51">
-        <f t="shared" ca="1" si="0"/>
-        <v>41.887404655539839</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
+        <v>4188.740465553984</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6">
       <c r="A52" t="s">
-        <v>79</v>
+        <v>56</v>
       </c>
       <c r="B52" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="C52" t="s">
-        <v>79</v>
+        <v>56</v>
       </c>
       <c r="D52">
-        <v>40.394912290000001</v>
+        <v>40.39491229</v>
       </c>
       <c r="E52">
         <v>-3.70466513</v>
       </c>
       <c r="F52">
-        <f t="shared" ca="1" si="0"/>
-        <v>179.21644647502143</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
+        <v>17921.64464750214</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6">
       <c r="A53" t="s">
-        <v>81</v>
+        <v>57</v>
       </c>
       <c r="B53" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="C53" t="s">
-        <v>81</v>
+        <v>57</v>
       </c>
       <c r="D53">
         <v>41.44963044</v>
       </c>
       <c r="E53">
-        <v>2.1984899640000002</v>
+        <v>2.198489964</v>
       </c>
       <c r="F53">
-        <f t="shared" ca="1" si="0"/>
-        <v>142.30237009671589</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
+        <v>14230.23700967159</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6">
       <c r="A54" t="s">
-        <v>82</v>
+        <v>58</v>
       </c>
       <c r="B54" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="C54" t="s">
-        <v>82</v>
+        <v>58</v>
       </c>
       <c r="D54">
-        <v>37.371729760000001</v>
+        <v>37.37172976</v>
       </c>
       <c r="E54">
-        <v>-6.0156183519999997</v>
+        <v>-6.015618352</v>
       </c>
       <c r="F54">
-        <f t="shared" ca="1" si="0"/>
-        <v>101.77260153129291</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
+        <v>10177.26015312929</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6">
       <c r="A55" t="s">
-        <v>83</v>
+        <v>59</v>
       </c>
       <c r="B55" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="C55" t="s">
-        <v>83</v>
+        <v>59</v>
       </c>
       <c r="D55">
-        <v>41.679906899999999</v>
+        <v>41.6799069</v>
       </c>
       <c r="E55">
-        <v>-0.87759162459999995</v>
+        <v>-0.8775916246</v>
       </c>
       <c r="F55">
-        <f t="shared" ca="1" si="0"/>
-        <v>127.63425146693545</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
+        <v>12763.42514669355</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6">
       <c r="A56" t="s">
-        <v>84</v>
+        <v>60</v>
       </c>
       <c r="B56" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="C56" t="s">
-        <v>84</v>
+        <v>60</v>
       </c>
       <c r="D56">
-        <v>36.713067330000001</v>
+        <v>36.71306733</v>
       </c>
       <c r="E56">
-        <v>-4.4577621350000003</v>
+        <v>-4.457762135</v>
       </c>
       <c r="F56">
-        <f t="shared" ca="1" si="0"/>
-        <v>168.15857227062156</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
+        <v>16815.85722706216</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6">
       <c r="A57" t="s">
-        <v>85</v>
+        <v>61</v>
       </c>
       <c r="B57" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="C57" t="s">
-        <v>85</v>
+        <v>61</v>
       </c>
       <c r="D57">
-        <v>59.301907649999997</v>
+        <v>59.30190765</v>
       </c>
       <c r="E57">
         <v>18.02080784</v>
       </c>
       <c r="F57">
-        <f t="shared" ca="1" si="0"/>
-        <v>113.09538916292749</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
+        <v>11309.53891629275</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6">
       <c r="A58" t="s">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="B58" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="C58" t="s">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="D58">
-        <v>57.697725740000003</v>
+        <v>57.69772574</v>
       </c>
       <c r="E58">
-        <v>11.995542220000001</v>
+        <v>11.99554222</v>
       </c>
       <c r="F58">
-        <f t="shared" ca="1" si="0"/>
-        <v>75.892270416072407</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
+        <v>7589.227041607241</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6">
       <c r="A59" t="s">
-        <v>88</v>
+        <v>63</v>
       </c>
       <c r="B59" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C59" t="s">
-        <v>88</v>
+        <v>63</v>
       </c>
       <c r="D59">
         <v>47.41204621</v>
       </c>
       <c r="E59">
-        <v>8.5743769469999993</v>
+        <v>8.574376946999999</v>
       </c>
       <c r="F59">
-        <f t="shared" ca="1" si="0"/>
-        <v>25.062922766098339</v>
+        <v>2506.292276609834</v>
       </c>
     </row>
   </sheetData>
